--- a/business_forms/049_ntouch_salon_spa_covid_19_questionnaire_and_important_appointment_information--business_forms.xlsx
+++ b/business_forms/049_ntouch_salon_spa_covid_19_questionnaire_and_important_appointment_information--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1152,8 +1152,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'option_6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Option 6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'option_7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Option 7'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'option_8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Option 8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'option_9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Option 9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'option_10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Option 10'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'option_11'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Option 11'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'option_12'}</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Option 12'}</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'option_13'}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Option 13'}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'option_14'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Option 14'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'option_15'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Option 15'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'option_16'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Option 16'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'option_17'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Option 17'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'option_18'}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Option 18'}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'option_19'}</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Option 19'}</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'option_20'}</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Option 20'}</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'option_21'}</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Option 21'}</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'option_22'}</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Option 22'}</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'option_23'}</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Option 23'}</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'option_24'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Option 24'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'option_25'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Option 25'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'option_24'}</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Option 24'}</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'option_25'}</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Option 25'}</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'option_26'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Option 26'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'option_26'}</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'Option 26'}</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'option_27'}</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'Option 27'}</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'option_28'}</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'Option 28'}</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'option_29'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Option 29'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'option_30'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Option 30'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'option_31'}</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Option 31'}</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'option_29'}</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'Option 29'}</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'option_30'}</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Option 30'}</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'option_32'}</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Option 32'}</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'option_33'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'Option 33'}</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'option_34'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'Option 34'}</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'option_35'}</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'Option 35'}</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'option_33'}</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'Option 33'}</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'option_34'}</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'Option 34'}</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_'option_36'}</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': 'Option 36'}</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
